--- a/public/data/contract_government_charges.xlsx
+++ b/public/data/contract_government_charges.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,13 +424,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>e61a0906-1193-4695-acc8-6a64cde86a24</v>
+        <v>68298850-cf51-4338-8a31-b344269a7197</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -447,16 +447,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>7087a69d-8146-4a53-8490-9032a28f5033</v>
+        <v>777b2047-7507-4674-94c5-4aa2eeb24587</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E3" t="str">
         <v>Government_charges</v>
@@ -470,16 +470,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>127d530d-8429-4b41-a80a-e5b2291bd3d3</v>
+        <v>11df087b-673e-444c-8236-31e9aa8fea67</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E4" t="str">
         <v>Government_charges</v>
@@ -488,21 +488,21 @@
         <v>3.5</v>
       </c>
       <c r="G4" t="str">
-        <v>Per pax excluding GST</v>
+        <v>Return per pax excluding GST</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>099dc3d1-17f0-4e26-a6d3-5031a34a8582</v>
+        <v>1bff4627-bf72-4d2c-869f-e9692103b6f5</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E5" t="str">
         <v>Government_charges</v>
@@ -511,21 +511,21 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="str">
-        <v>Standard government levy</v>
+        <v>Return per pax excluding GST</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>30ef54d5-9422-40a2-a8b9-811fd571d20b</v>
+        <v>8d103063-493a-4fcc-9afa-72cd4344dda2</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E6" t="str">
         <v>Government_charges</v>
@@ -539,39 +539,39 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ed381f35-805a-4e6f-b961-44cff3586ccc</v>
+        <v>fbfea8fa-7e37-4302-9e8c-4b9da9fcb1d3</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-007-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E7" t="str">
         <v>Government_charges</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="str">
-        <v>Speedboat lower levy</v>
+        <v>Return per pax excluding GST</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4d9390d5-550b-4ffa-9d7d-f30ade21a9f1</v>
+        <v>2e9fbb80-08c5-460e-bc4e-9d9c82cb1dd7</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-004-001</v>
       </c>
       <c r="E8" t="str">
         <v>Government_charges</v>
@@ -580,58 +580,288 @@
         <v>3.5</v>
       </c>
       <c r="G8" t="str">
-        <v>Per pax excluding GST</v>
+        <v>Return per pax excluding GST</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8fe074fc-7763-404a-a520-c9bd01088372</v>
+        <v>814cc44e-2800-4e16-8edf-1f6de58f1ecb</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E9" t="str">
         <v>Government_charges</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="str">
-        <v>Speedboat levy</v>
+        <v>Return per pax excluding GST</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>d9d8fa44-1385-4ffa-9725-085a9462e859</v>
+        <v>63bcb46d-f0c8-49c9-888b-152c7de85629</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
+        <v>CTR-005-002</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F10">
+        <v>3.5</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>a04efa8e-7869-43d7-816c-bfedffefba2e</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D11" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F11">
+        <v>3.5</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>0d324c6c-b306-4a9c-9d1a-196f1b96125d</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F12">
+        <v>3.5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>39f909e9-4642-48bd-a7b8-eeebf45e0055</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F13">
+        <v>3.5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>e8545051-87a6-403b-a792-8ac586a6caf3</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D14" t="str">
+        <v>CTR-007-001</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Speedboat lower levy</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>b5f9efad-c4ed-4009-b4d1-2ac0c58449be</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-007-002</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F15">
+        <v>3.5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>f394e4a5-2878-47a2-bd52-028ecdd699f0</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F16">
+        <v>3.5</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>6a339645-b8e9-46fe-b358-7ed166e600b9</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F17">
+        <v>3.5</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>0ca0e74c-e3ab-4b26-a58b-ead0d5a4700f</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Speedboat lower levy</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>dfded33e-6e95-4bf2-9a46-88af0306ce59</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
         <v>CTR-010-001</v>
       </c>
-      <c r="E10" t="str">
-        <v>Government_charges</v>
-      </c>
-      <c r="F10">
-        <v>3.5</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Per pax excluding GST</v>
+      <c r="E19" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F19">
+        <v>3.5</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Return per pax excluding GST</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>26c7a169-541b-4d09-8827-99f57605c6ec</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CTR-010-002</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Government_charges</v>
+      </c>
+      <c r="F20">
+        <v>3.5</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Return per pax excluding GST</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
   </ignoredErrors>
 </worksheet>
 </file>